--- a/outputs_xlsx_solution/test_new4.4-wide-NR-4.xlsx
+++ b/outputs_xlsx_solution/test_new4.4-wide-NR-4.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>fadd F2, F2, F3</t>
   </si>
   <si>
@@ -144,6 +147,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -684,7 +690,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -704,13 +710,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -730,13 +736,16 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -756,13 +765,19 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
       </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -785,10 +800,10 @@
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -808,10 +823,10 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I7" t="s">
         <v>14</v>
@@ -823,7 +838,7 @@
         <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -843,10 +858,10 @@
         <v>9</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -858,7 +873,7 @@
         <v>14</v>
       </c>
       <c r="M8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -878,7 +893,7 @@
         <v>9</v>
       </c>
       <c r="I9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J9" t="s">
         <v>14</v>
@@ -893,7 +908,7 @@
         <v>14</v>
       </c>
       <c r="N9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -904,7 +919,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -913,7 +928,7 @@
         <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N10" t="s">
         <v>14</v>
@@ -925,7 +940,7 @@
         <v>14</v>
       </c>
       <c r="Q10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -936,7 +951,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -945,19 +960,19 @@
         <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L11" t="s">
         <v>14</v>
       </c>
       <c r="M11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -977,19 +992,19 @@
         <v>9</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N12" t="s">
         <v>14</v>
       </c>
       <c r="O12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1000,7 +1015,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -1009,16 +1024,16 @@
         <v>9</v>
       </c>
       <c r="M13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N13" t="s">
         <v>14</v>
       </c>
       <c r="O13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -1029,7 +1044,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -1038,19 +1053,19 @@
         <v>9</v>
       </c>
       <c r="N14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q14" t="s">
         <v>14</v>
       </c>
       <c r="R14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -1061,7 +1076,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -1070,13 +1085,13 @@
         <v>9</v>
       </c>
       <c r="Q15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R15" t="s">
         <v>14</v>
       </c>
       <c r="S15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1108,7 +1123,7 @@
         <v>14</v>
       </c>
       <c r="Y16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1119,7 +1134,7 @@
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S17" t="s">
         <v>5</v>
@@ -1128,7 +1143,7 @@
         <v>9</v>
       </c>
       <c r="U17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y17" t="s">
         <v>14</v>
@@ -1140,7 +1155,7 @@
         <v>14</v>
       </c>
       <c r="AB17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1151,7 +1166,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S18" t="s">
         <v>5</v>
@@ -1163,10 +1178,10 @@
         <v>14</v>
       </c>
       <c r="V18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1186,16 +1201,16 @@
         <v>9</v>
       </c>
       <c r="U19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V19" t="s">
         <v>14</v>
       </c>
       <c r="W19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -1206,7 +1221,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T20" t="s">
         <v>5</v>
@@ -1215,22 +1230,22 @@
         <v>9</v>
       </c>
       <c r="V20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="s">
         <v>14</v>
       </c>
       <c r="Z20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1241,7 +1256,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T21" t="s">
         <v>5</v>
@@ -1250,19 +1265,19 @@
         <v>9</v>
       </c>
       <c r="Y21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB21" t="s">
         <v>14</v>
       </c>
       <c r="AC21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1273,7 +1288,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T22" t="s">
         <v>5</v>
@@ -1282,13 +1297,13 @@
         <v>9</v>
       </c>
       <c r="AB22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC22" t="s">
         <v>14</v>
       </c>
       <c r="AD22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1320,7 +1335,7 @@
         <v>14</v>
       </c>
       <c r="AF23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -1331,7 +1346,7 @@
         <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U24" t="s">
         <v>5</v>
@@ -1340,7 +1355,7 @@
         <v>9</v>
       </c>
       <c r="AB24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF24" t="s">
         <v>14</v>
@@ -1352,7 +1367,7 @@
         <v>14</v>
       </c>
       <c r="AI24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -1363,7 +1378,7 @@
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U25" t="s">
         <v>5</v>
@@ -1375,10 +1390,10 @@
         <v>14</v>
       </c>
       <c r="AD25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -1398,19 +1413,19 @@
         <v>9</v>
       </c>
       <c r="AC26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE26" t="s">
         <v>14</v>
       </c>
       <c r="AF26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -1421,7 +1436,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V27" t="s">
         <v>5</v>
@@ -1430,19 +1445,19 @@
         <v>9</v>
       </c>
       <c r="AD27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF27" t="s">
         <v>14</v>
       </c>
       <c r="AG27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -1453,7 +1468,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V28" t="s">
         <v>5</v>
@@ -1462,19 +1477,19 @@
         <v>9</v>
       </c>
       <c r="AF28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI28" t="s">
         <v>14</v>
       </c>
       <c r="AJ28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1485,7 +1500,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V29" t="s">
         <v>5</v>
@@ -1494,13 +1509,13 @@
         <v>9</v>
       </c>
       <c r="AI29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ29" t="s">
         <v>14</v>
       </c>
       <c r="AK29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -1532,7 +1547,7 @@
         <v>14</v>
       </c>
       <c r="AM30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -1543,7 +1558,7 @@
         <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W31" t="s">
         <v>5</v>
@@ -1552,7 +1567,7 @@
         <v>9</v>
       </c>
       <c r="AI31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM31" t="s">
         <v>14</v>
@@ -1564,7 +1579,7 @@
         <v>14</v>
       </c>
       <c r="AP31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -1575,7 +1590,7 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W32" t="s">
         <v>5</v>
@@ -1587,10 +1602,10 @@
         <v>14</v>
       </c>
       <c r="AK32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -1610,19 +1625,19 @@
         <v>9</v>
       </c>
       <c r="AJ33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL33" t="s">
         <v>14</v>
       </c>
       <c r="AM33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -1633,7 +1648,7 @@
         <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X34" t="s">
         <v>5</v>
@@ -1642,19 +1657,19 @@
         <v>9</v>
       </c>
       <c r="AK34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM34" t="s">
         <v>14</v>
       </c>
       <c r="AN34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -1665,7 +1680,7 @@
         <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X35" t="s">
         <v>5</v>
@@ -1674,19 +1689,19 @@
         <v>9</v>
       </c>
       <c r="AM35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP35" t="s">
         <v>14</v>
       </c>
       <c r="AQ35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -1697,7 +1712,7 @@
         <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X36" t="s">
         <v>5</v>
@@ -1706,13 +1721,13 @@
         <v>9</v>
       </c>
       <c r="AP36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ36" t="s">
         <v>14</v>
       </c>
       <c r="AR36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
@@ -1744,7 +1759,7 @@
         <v>14</v>
       </c>
       <c r="AT37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
@@ -1755,7 +1770,7 @@
         <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y38" t="s">
         <v>5</v>
@@ -1764,7 +1779,7 @@
         <v>9</v>
       </c>
       <c r="AP38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT38" t="s">
         <v>14</v>
@@ -1776,7 +1791,7 @@
         <v>14</v>
       </c>
       <c r="AW38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
@@ -1787,7 +1802,7 @@
         <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y39" t="s">
         <v>5</v>
@@ -1799,10 +1814,10 @@
         <v>14</v>
       </c>
       <c r="AR39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -1822,19 +1837,19 @@
         <v>9</v>
       </c>
       <c r="AQ40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS40" t="s">
         <v>14</v>
       </c>
       <c r="AT40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
@@ -1845,7 +1860,7 @@
         <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB41" t="s">
         <v>5</v>
@@ -1854,19 +1869,19 @@
         <v>9</v>
       </c>
       <c r="AR41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT41" t="s">
         <v>14</v>
       </c>
       <c r="AU41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -1877,7 +1892,7 @@
         <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB42" t="s">
         <v>5</v>
@@ -1886,19 +1901,19 @@
         <v>9</v>
       </c>
       <c r="AT42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW42" t="s">
         <v>14</v>
       </c>
       <c r="AX42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -1909,7 +1924,7 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB43" t="s">
         <v>5</v>
@@ -1918,13 +1933,13 @@
         <v>9</v>
       </c>
       <c r="AW43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX43" t="s">
         <v>14</v>
       </c>
       <c r="AY43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
@@ -1935,7 +1950,7 @@
         <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY44" t="s">
         <v>5</v>
@@ -1947,12 +1962,12 @@
         <v>14</v>
       </c>
       <c r="BB44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
@@ -1960,7 +1975,7 @@
         <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -1968,15 +1983,15 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
@@ -1984,39 +1999,55 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" t="s">
         <v>35</v>
       </c>
-      <c r="B54" t="s">
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
         <v>36</v>
+      </c>
+      <c r="B55" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
